--- a/virtual-physics-lab/app/dl/ASRJC_Q3_container.xlsx
+++ b/virtual-physics-lab/app/dl/ASRJC_Q3_container.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -91,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -99,6 +101,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -224,6 +227,7 @@
           </marker>
           <trendline>
             <trendlineType val="poly"/>
+            <order val="2"/>
             <dispRSqr val="1"/>
             <dispEq val="1"/>
           </trendline>
@@ -686,99 +690,99 @@
       <c r="A6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -870,34 +874,34 @@
       <c r="A6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <f>(B6+C6)/2</f>
         <v/>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <f>COS(RADIANS(D6))^2</f>
         <v/>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="8">
         <f>IF(A6&gt;0,E6*((4.52/2)^2+A6^2)/A6,"")</f>
         <v/>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>max θ (from data)</t>
         </is>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="8">
         <f>MAX(D6:D12)</f>
         <v/>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>°</t>
         </is>
@@ -907,21 +911,21 @@
       <c r="A7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="8">
         <f>(B7+C7)/2</f>
         <v/>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <f>COS(RADIANS(D7))^2</f>
         <v/>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <f>IF(A7&gt;0,E7*((4.52/2)^2+A7^2)/A7,"")</f>
         <v/>
       </c>
@@ -930,21 +934,21 @@
       <c r="A8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <f>(B8+C8)/2</f>
         <v/>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <f>COS(RADIANS(D8))^2</f>
         <v/>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <f>IF(A8&gt;0,E8*((4.52/2)^2+A8^2)/A8,"")</f>
         <v/>
       </c>
@@ -953,21 +957,21 @@
       <c r="A9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <f>(B9+C9)/2</f>
         <v/>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <f>COS(RADIANS(D9))^2</f>
         <v/>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="8">
         <f>IF(A9&gt;0,E9*((4.52/2)^2+A9^2)/A9,"")</f>
         <v/>
       </c>
@@ -976,21 +980,21 @@
       <c r="A10" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="8">
         <f>(B10+C10)/2</f>
         <v/>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <f>COS(RADIANS(D10))^2</f>
         <v/>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <f>IF(A10&gt;0,E10*((4.52/2)^2+A10^2)/A10,"")</f>
         <v/>
       </c>
@@ -999,21 +1003,21 @@
       <c r="A11" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="8">
         <f>(B11+C11)/2</f>
         <v/>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <f>COS(RADIANS(D11))^2</f>
         <v/>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <f>IF(A11&gt;0,E11*((4.52/2)^2+A11^2)/A11,"")</f>
         <v/>
       </c>
@@ -1022,21 +1026,21 @@
       <c r="A12" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="8">
         <f>(B12+C12)/2</f>
         <v/>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="8">
         <f>COS(RADIANS(D12))^2</f>
         <v/>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="8">
         <f>IF(A12&gt;0,E12*((4.52/2)^2+A12^2)/A12,"")</f>
         <v/>
       </c>
